--- a/BI_Team_Status.xlsx
+++ b/BI_Team_Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Squard_BI_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FDA6C1-B23E-42CD-A743-893280A7D3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CC82CE-2ECF-4A60-A119-C1DD692DCCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{895920EF-5F4F-47FE-BD4C-67B9399B4943}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{895920EF-5F4F-47FE-BD4C-67B9399B4943}"/>
   </bookViews>
   <sheets>
     <sheet name="Santhosh" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="31">
   <si>
     <t>Git Commands</t>
   </si>
@@ -110,6 +110,24 @@
   </si>
   <si>
     <t>In progress</t>
+  </si>
+  <si>
+    <t>Testing process video</t>
+  </si>
+  <si>
+    <t>virtual environment setup in pycharm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created folder in pycharm </t>
+  </si>
+  <si>
+    <t>Azure tutorial video</t>
+  </si>
+  <si>
+    <t>basic services exploration</t>
+  </si>
+  <si>
+    <t>Terraform code for azure virtual machines understanding</t>
   </si>
 </sst>
 </file>
@@ -140,12 +158,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -160,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -169,6 +193,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966D5208-BAAF-48FD-B102-C0B4EDBFFAE1}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.109375" customWidth="1"/>
@@ -639,6 +667,35 @@
         <v>24</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -646,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA8939A-A13F-4E6F-B704-24FCC4BDCF06}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5546875" customWidth="1"/>
@@ -794,6 +851,35 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/BI_Team_Status.xlsx
+++ b/BI_Team_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Squard_BI_Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CC82CE-2ECF-4A60-A119-C1DD692DCCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF2536-7911-41A3-B06B-20892E530EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{895920EF-5F4F-47FE-BD4C-67B9399B4943}"/>
   </bookViews>
@@ -158,7 +158,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,6 +168,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -184,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -197,6 +203,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966D5208-BAAF-48FD-B102-C0B4EDBFFAE1}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.109375" customWidth="1"/>
@@ -692,9 +700,12 @@
       <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="B26" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
